--- a/data/5_results/no_prompt/result_llama_no_prompt_6.xlsx
+++ b/data/5_results/no_prompt/result_llama_no_prompt_6.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sem</t>
+          <t>fuzzy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0,996</t>
+          <t>0,868</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,869</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0,994</t>
+          <t>0,868</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,864</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,401</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,388</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0,995</t>
+          <t>0,810</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,429</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,742</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0,999</t>
+          <t>0,751</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0,999</t>
+          <t>0,705</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,680</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0,997</t>
+          <t>0,621</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0,996</t>
+          <t>0,619</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,737</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0,982</t>
+          <t>0,782</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0,983</t>
+          <t>0,784</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0,978</t>
+          <t>0,309</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0,975</t>
+          <t>0,305</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0,999</t>
+          <t>0,640</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0,995</t>
+          <t>0,487</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,498</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0,998</t>
+          <t>0,549</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0,997</t>
+          <t>0,770</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,290</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0,968</t>
+          <t>0,388</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0,987</t>
+          <t>0,348</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0,979</t>
+          <t>0,359</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0,996</t>
+          <t>0,463</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0,995</t>
+          <t>0,402</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0,981</t>
+          <t>0,634</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,617</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,491</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0,999</t>
+          <t>0,630</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,427</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,721</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0,997</t>
+          <t>0,094</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0,975</t>
+          <t>0,582</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0,995</t>
+          <t>0,482</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0,996</t>
+          <t>0,820</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,830</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,427</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0,989</t>
+          <t>0,305</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0,964</t>
+          <t>0,067</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0,889</t>
+          <t>0,310</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,307</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0,987</t>
+          <t>0,483</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0,851</t>
+          <t>0,083</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0,994</t>
+          <t>0,209</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0,977</t>
+          <t>0,028</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0,989</t>
+          <t>0,216</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0,966</t>
+          <t>0,250</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0,992</t>
+          <t>0,298</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0,993</t>
+          <t>0,182</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,125</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0,981</t>
+          <t>0,308</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0,695</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0,897</t>
+          <t>0,438</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3321,10 +3321,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F1 (Simple)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SEM</t>
+          <t>F1 (Weighted)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>W F1</t>
+          <t>Fuzzy (Simple)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>W SEM</t>
+          <t>Fuzzy (Weighted)</t>
         </is>
       </c>
     </row>
@@ -3367,17 +3367,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0,967</t>
+          <t>0,760</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0,760</t>
+          <t>0,471</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0,994</t>
+          <t>0,642</t>
         </is>
       </c>
     </row>

--- a/data/5_results/no_prompt/result_llama_no_prompt_6.xlsx
+++ b/data/5_results/no_prompt/result_llama_no_prompt_6.xlsx
@@ -435,11 +435,11 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>sem</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -502,42 +502,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0,924</t>
+          <t>0,182</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0,935</t>
+          <t>0,192</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0,930</t>
+          <t>0,187</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0,868</t>
+          <t>0,859</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3673,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3435</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>283</v>
+        <v>45</v>
       </c>
       <c r="J2" t="n">
-        <v>238</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -548,42 +548,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0,927</t>
+          <t>0,815</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0,932</t>
+          <t>0,846</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0,930</t>
+          <t>0,830</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0,869</t>
+          <t>0,962</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3606,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3362</v>
+        <v>44</v>
       </c>
       <c r="I3" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>244</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -594,42 +594,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0,926</t>
+          <t>0,176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0,933</t>
+          <t>0,180</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0,930</t>
+          <t>0,178</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0,868</t>
+          <t>0,886</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3573,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3333</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>265</v>
+        <v>42</v>
       </c>
       <c r="J4" t="n">
-        <v>240</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -640,42 +640,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0,926</t>
+          <t>0,788</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0,928</t>
+          <t>0,820</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0,927</t>
+          <t>0,804</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0,864</t>
+          <t>0,958</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3505,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3253</v>
+        <v>41</v>
       </c>
       <c r="I5" t="n">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>252</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -686,42 +686,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0,566</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0,578</t>
+          <t>0,490</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0,572</t>
+          <t>0,495</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0,401</t>
+          <t>0,752</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3479,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2012</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>1541</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>1467</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -732,42 +732,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0,554</t>
+          <t>0,383</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0,564</t>
+          <t>0,400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0,559</t>
+          <t>0,391</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0,388</t>
+          <t>0,711</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3409,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1921</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>1546</v>
+        <v>29</v>
       </c>
       <c r="J7" t="n">
-        <v>1488</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -778,42 +778,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0,858</t>
+          <t>0,595</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0,936</t>
+          <t>0,733</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0,895</t>
+          <t>0,657</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0,810</t>
+          <t>0,919</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2442,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2285</v>
+        <v>44</v>
       </c>
       <c r="I8" t="n">
-        <v>378</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>157</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -824,42 +824,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0,581</t>
+          <t>0,483</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0,621</t>
+          <t>0,609</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0,600</t>
+          <t>0,538</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0,429</t>
+          <t>0,826</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2159,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1340</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>968</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>819</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -870,42 +870,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0,832</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0,873</t>
+          <t>0,070</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0,852</t>
+          <t>0,128</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0,742</t>
+          <t>0,843</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2032,000</t>
+          <t>43,000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1773</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>357</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>259</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -916,42 +916,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0,844</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0,871</t>
+          <t>0,095</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0,858</t>
+          <t>0,174</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0,751</t>
+          <t>0,095</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2015,000</t>
+          <t>42,000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1756</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>259</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -962,42 +962,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0,801</t>
+          <t>0,710</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0,855</t>
+          <t>0,564</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0,827</t>
+          <t>0,629</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0,705</t>
+          <t>0,948</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1934,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1654</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>411</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>280</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -1008,42 +1008,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0,774</t>
+          <t>0,727</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0,848</t>
+          <t>0,600</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0,809</t>
+          <t>0,658</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0,680</t>
+          <t>0,965</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1931,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0,30</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1638</v>
+        <v>24</v>
       </c>
       <c r="I13" t="n">
-        <v>478</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
-        <v>293</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1054,42 +1054,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0,718</t>
+          <t>0,586</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0,821</t>
+          <t>0,654</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0,766</t>
+          <t>0,618</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0,621</t>
+          <t>0,952</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1808,000</t>
+          <t>26,000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1485</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>583</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>323</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1100,42 +1100,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0,717</t>
+          <t>0,633</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0,819</t>
+          <t>0,704</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0,765</t>
+          <t>0,667</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0,619</t>
+          <t>0,954</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1800,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1475</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>581</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>325</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1146,42 +1146,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0,821</t>
+          <t>0,677</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0,877</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0,848</t>
+          <t>0,724</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0,737</t>
+          <t>0,975</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1761,000</t>
+          <t>54,000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1545</v>
+        <v>42</v>
       </c>
       <c r="I16" t="n">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>216</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -1192,42 +1192,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0,864</t>
+          <t>0,517</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0,892</t>
+          <t>0,682</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0,878</t>
+          <t>0,588</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0,782</t>
+          <t>0,707</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1342,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1197</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
-        <v>145</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1238,42 +1238,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0,864</t>
+          <t>0,533</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0,894</t>
+          <t>0,696</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0,879</t>
+          <t>0,604</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0,784</t>
+          <t>0,883</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1336,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1195</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>188</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>141</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1284,42 +1284,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0,463</t>
+          <t>0,136</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0,482</t>
+          <t>0,120</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,472</t>
+          <t>0,128</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0,309</t>
+          <t>0,656</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1358,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>654</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>759</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>704</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1330,42 +1330,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>0,200</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0,158</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0,176</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>0,453</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0,483</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0,467</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0,305</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1261,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0,20</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>609</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>736</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>652</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1376,42 +1376,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0,727</t>
+          <t>0,628</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0,843</t>
+          <t>0,794</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0,781</t>
+          <t>0,701</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0,640</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>897,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>756</v>
+        <v>27</v>
       </c>
       <c r="I21" t="n">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>141</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -1422,42 +1422,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0,564</t>
+          <t>0,286</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0,781</t>
+          <t>0,667</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0,655</t>
+          <t>0,400</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0,487</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>785,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>613</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>473</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>172</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1468,42 +1468,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0,681</t>
+          <t>0,222</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0,650</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0,665</t>
+          <t>0,308</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0,498</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>692,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>450</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>211</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1514,42 +1514,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0,623</t>
+          <t>0,571</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0,823</t>
+          <t>0,800</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0,709</t>
+          <t>0,667</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0,549</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>447</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1560,42 +1560,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0,890</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0,852</t>
+          <t>0,903</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0,870</t>
+          <t>0,836</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0,770</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>539,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>459</v>
+        <v>28</v>
       </c>
       <c r="I25" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0,645</t>
+          <t>0,667</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0,345</t>
+          <t>0,400</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0,450</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0,290</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>426,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>279</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1652,42 +1652,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0,600</t>
+          <t>0,231</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0,524</t>
+          <t>0,176</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0,559</t>
+          <t>0,200</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0,388</t>
+          <t>0,847</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>481,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>252</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>229</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1698,42 +1698,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0,639</t>
+          <t>0,273</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0,433</t>
+          <t>0,375</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0,516</t>
+          <t>0,316</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0,348</t>
+          <t>0,897</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>367,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>208</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1744,42 +1744,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0,658</t>
+          <t>0,714</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0,442</t>
+          <t>0,833</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0,528</t>
+          <t>0,769</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0,359</t>
+          <t>0,984</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>505,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>223</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>282</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1790,42 +1790,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0,670</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0,600</t>
+          <t>0,857</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0,633</t>
+          <t>0,800</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0,463</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>427,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>256</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1836,42 +1836,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0,567</t>
+          <t>0,018</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0,580</t>
+          <t>0,048</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0,573</t>
+          <t>0,026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0,402</t>
+          <t>0,131</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>426,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="J31" t="n">
-        <v>179</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1882,42 +1882,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0,698</t>
+          <t>0,143</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0,872</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0,776</t>
+          <t>0,250</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0,634</t>
+          <t>0,143</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>287</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1928,42 +1928,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0,817</t>
+          <t>0,364</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0,716</t>
+          <t>0,571</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0,763</t>
+          <t>0,444</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0,617</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>299,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1974,42 +1974,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0,751</t>
+          <t>0,583</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0,587</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0,659</t>
+          <t>0,667</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0,491</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>293,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>121</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2020,42 +2020,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0,766</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0,779</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0,773</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0,630</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>226</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2066,42 +2066,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0,787</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0,483</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0,598</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0,427</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2112,42 +2112,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0,807</t>
+          <t>0,429</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0,872</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0,838</t>
+          <t>0,545</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0,721</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>251</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2158,42 +2158,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0,204</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0,149</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0,172</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0,094</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="J38" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2204,42 +2204,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0,631</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0,884</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0,736</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0,582</t>
+          <t>0,813</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>232,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J39" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2250,42 +2250,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0,640</t>
+          <t>0,333</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0,662</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0,651</t>
+          <t>0,400</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0,482</t>
+          <t>0,897</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>204,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2296,42 +2296,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0,896</t>
+          <t>0,818</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0,906</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0,901</t>
+          <t>0,900</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0,820</t>
+          <t>0,818</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>191,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>173</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2342,27 +2342,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0,905</t>
+          <t>0,818</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0,910</t>
+          <t>0,900</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0,907</t>
+          <t>0,857</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0,830</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2388,42 +2388,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0,844</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0,463</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0,598</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0,427</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2434,42 +2434,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0,420</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0,527</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0,467</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0,305</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2480,42 +2480,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0,394</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0,075</t>
+          <t>0,056</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0,126</t>
+          <t>0,100</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0,067</t>
+          <t>0,662</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>173,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>160</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -2526,42 +2526,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0,434</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0,520</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0,473</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0,310</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>127,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -2572,88 +2572,94 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0,484</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0,455</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0,469</t>
+          <t>0,600</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0,307</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>101,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tpa</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0,675</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0,629</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0,651</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0,483</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>56</v>
-      </c>
-      <c r="I48" t="n">
-        <v>27</v>
-      </c>
-      <c r="J48" t="n">
-        <v>33</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -2664,42 +2670,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0,270</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0,106</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0,153</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0,083</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>94,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -2710,134 +2716,146 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0,391</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0,310</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0,346</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0,209</t>
+          <t>0,178</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>87,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>posterior crossbite</t>
+          <t>Posterior Crossbite</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0,273</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0,030</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0,055</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0,028</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" t="n">
-        <v>8</v>
-      </c>
-      <c r="J51" t="n">
-        <v>96</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>lower banding</t>
+          <t>Lower Banding</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0,410</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0,314</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0,356</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0,216</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>16</v>
-      </c>
-      <c r="I52" t="n">
-        <v>23</v>
-      </c>
-      <c r="J52" t="n">
-        <v>35</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -2848,42 +2866,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0,519</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0,326</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0,400</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0,250</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>86,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2894,42 +2912,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0,474</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0,444</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0,459</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0,298</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2940,27 +2958,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0,267</t>
+          <t>0,500</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0,364</t>
+          <t>0,250</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0,308</t>
+          <t>0,333</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0,182</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2969,59 +2987,65 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>anterior crossbite</t>
+          <t>Anterior Crossbite</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0,667</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0,133</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0,222</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0,125</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>4</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>26</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3032,134 +3056,146 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0,432</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,516</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0,471</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0,308</t>
+          <t>0,178</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>mandibular advancement appliance</t>
+          <t>Mandibular Advancement Appliance</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>6</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nance</t>
+          <t>NANCE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0,875</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0,467</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0,609</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0,438</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" t="n">
-        <v>8</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3217,93 +3253,105 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tongue crib</t>
+          <t>Tongue Crib</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>8</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>facemask</t>
+          <t>FaceMask</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0,143</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0,250</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0,143</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>6</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3321,10 +3369,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3335,22 +3383,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>F1 (Simple)</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>F1 (Weighted)</t>
+          <t>SEM</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fuzzy (Simple)</t>
+          <t>W F1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Fuzzy (Weighted)</t>
+          <t>W SEM</t>
         </is>
       </c>
     </row>
@@ -3362,22 +3410,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0,598</t>
+          <t>0,415</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0,760</t>
+          <t>0,786</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0,471</t>
+          <t>0,494</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0,642</t>
+          <t>0,823</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3488,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6419</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5">
@@ -3450,7 +3498,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>142</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
